--- a/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-tiflow-diga-receipt-bundle.xlsx
+++ b/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-tiflow-diga-receipt-bundle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5212" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5238" uniqueCount="397">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -271,8 +271,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -387,6 +387,16 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -489,6 +499,9 @@
 This specification defines some specific uses of Bundle.link for [searching](http://hl7.org/fhir/R4/search.html#conformance) and [paging](http://hl7.org/fhir/R4/http.html#paging), but no specific uses for Bundle.entry.link, and no defined function in a transaction - the meaning is implementation specific.</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.id</t>
   </si>
   <si>
@@ -505,9 +518,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -528,6 +538,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -564,6 +584,9 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -571,6 +594,9 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -592,8 +618,8 @@
     <t>closed</t>
   </si>
   <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -642,6 +668,9 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -651,8 +680,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-2
-</t>
+    <t>ele-1
+bdl-2</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -708,8 +737,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-3
-</t>
+    <t>ele-1
+bdl-3</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -763,6 +792,9 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -790,8 +822,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-4
-</t>
+    <t>ele-1
+bdl-4</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1574,15 +1606,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="57.64453125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2371,30 +2403,30 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2420,13 +2452,13 @@
         <v>108</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2434,7 +2466,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>78</v>
@@ -2452,13 +2484,13 @@
         <v>78</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>78</v>
@@ -2476,7 +2508,7 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>88</v>
@@ -2500,15 +2532,15 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2531,16 +2563,16 @@
         <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2590,7 +2622,7 @@
         <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2611,18 +2643,18 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2645,16 +2677,16 @@
         <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2704,7 +2736,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2713,7 +2745,7 @@
         <v>88</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>100</v>
@@ -2733,10 +2765,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2759,16 +2791,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2818,7 +2850,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2827,7 +2859,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>100</v>
@@ -2836,7 +2868,7 @@
         <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>78</v>
@@ -2847,10 +2879,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2873,13 +2905,13 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2930,7 +2962,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2948,7 +2980,7 @@
         <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -2959,14 +2991,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2985,16 +3017,16 @@
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3032,19 +3064,19 @@
         <v>78</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3056,13 +3088,13 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3073,14 +3105,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3099,19 +3131,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3160,7 +3192,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3172,7 +3204,7 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -3189,10 +3221,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3215,15 +3247,17 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3272,7 +3306,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -3301,10 +3335,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3330,12 +3364,14 @@
         <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3384,7 +3420,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3413,10 +3449,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3424,7 +3460,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>80</v>
@@ -3439,13 +3475,13 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3484,17 +3520,17 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3503,16 +3539,16 @@
         <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3523,10 +3559,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3549,13 +3585,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3606,7 +3642,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3624,7 +3660,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3635,14 +3671,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3661,16 +3697,16 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3708,19 +3744,19 @@
         <v>78</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3732,13 +3768,13 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3749,14 +3785,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3775,19 +3811,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3836,7 +3872,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3848,7 +3884,7 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3865,10 +3901,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3894,10 +3930,10 @@
         <v>78</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3948,7 +3984,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3960,7 +3996,7 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
@@ -3977,10 +4013,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4006,13 +4042,13 @@
         <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4062,7 +4098,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4091,10 +4127,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4117,13 +4153,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4174,7 +4210,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4192,7 +4228,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4203,10 +4239,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4229,13 +4265,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4286,7 +4322,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4295,7 +4331,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -4304,7 +4340,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4315,10 +4351,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4341,13 +4377,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4398,7 +4434,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4416,7 +4452,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4427,14 +4463,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4453,16 +4489,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4500,19 +4536,19 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4524,13 +4560,13 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4541,14 +4577,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4567,19 +4603,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4628,7 +4664,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4640,7 +4676,7 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4657,10 +4693,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4686,13 +4722,13 @@
         <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4718,13 +4754,13 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -4742,7 +4778,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4771,10 +4807,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4797,16 +4833,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4856,7 +4892,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4885,10 +4921,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4911,13 +4947,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4968,7 +5004,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4977,7 +5013,7 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
@@ -4986,7 +5022,7 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -4997,10 +5033,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5023,13 +5059,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5080,7 +5116,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5098,7 +5134,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5109,14 +5145,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5135,16 +5171,16 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5182,19 +5218,19 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5206,13 +5242,13 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5223,14 +5259,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5249,19 +5285,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5310,7 +5346,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5322,7 +5358,7 @@
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -5339,10 +5375,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5368,10 +5404,10 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5398,13 +5434,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5422,7 +5458,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -5451,10 +5487,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5480,13 +5516,13 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5536,7 +5572,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -5565,10 +5601,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5591,15 +5627,17 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5648,7 +5686,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5677,10 +5715,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5703,15 +5741,17 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -5760,7 +5800,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5789,10 +5829,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5815,15 +5855,17 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5872,7 +5914,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5901,10 +5943,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5927,15 +5969,17 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -5984,7 +6028,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6013,10 +6057,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6039,13 +6083,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6096,7 +6140,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6105,7 +6149,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -6114,7 +6158,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6125,10 +6169,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6151,13 +6195,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6208,7 +6252,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6226,7 +6270,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6237,14 +6281,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6263,16 +6307,16 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6310,19 +6354,19 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6334,13 +6378,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6351,14 +6395,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6377,19 +6421,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6438,7 +6482,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6450,7 +6494,7 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -6467,10 +6511,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6493,15 +6537,17 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6550,7 +6596,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6579,10 +6625,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6608,12 +6654,14 @@
         <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -6662,7 +6710,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6691,10 +6739,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6717,16 +6765,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6776,7 +6824,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6805,10 +6853,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6831,16 +6879,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6890,7 +6938,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6919,10 +6967,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6945,16 +6993,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7004,7 +7052,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7022,7 +7070,7 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7033,13 +7081,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>78</v>
@@ -7061,13 +7109,13 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7118,7 +7166,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7127,16 +7175,16 @@
         <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7147,10 +7195,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7173,13 +7221,13 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7230,7 +7278,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7248,7 +7296,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7259,14 +7307,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7285,16 +7333,16 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7332,19 +7380,19 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7356,13 +7404,13 @@
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7373,14 +7421,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7399,19 +7447,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7460,7 +7508,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7472,7 +7520,7 @@
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -7489,10 +7537,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7518,10 +7566,10 @@
         <v>78</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7572,7 +7620,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7584,7 +7632,7 @@
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -7601,10 +7649,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7630,13 +7678,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7686,7 +7734,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7715,10 +7763,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7741,16 +7789,16 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7800,7 +7848,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7818,10 +7866,10 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -7829,10 +7877,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7855,13 +7903,13 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7912,7 +7960,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -7921,7 +7969,7 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
@@ -7930,7 +7978,7 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -7941,10 +7989,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7967,13 +8015,13 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8024,7 +8072,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8042,7 +8090,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8053,14 +8101,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8079,16 +8127,16 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8126,19 +8174,19 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8150,13 +8198,13 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8167,14 +8215,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8193,19 +8241,19 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8254,7 +8302,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8266,7 +8314,7 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -8283,10 +8331,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8312,13 +8360,13 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8344,13 +8392,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8368,7 +8416,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8397,10 +8445,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8423,16 +8471,16 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8482,7 +8530,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8511,10 +8559,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8537,13 +8585,13 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8594,7 +8642,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8603,7 +8651,7 @@
         <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>100</v>
@@ -8612,7 +8660,7 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -8623,10 +8671,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8649,13 +8697,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8706,7 +8754,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8724,7 +8772,7 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -8735,14 +8783,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8761,16 +8809,16 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8808,19 +8856,19 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -8832,13 +8880,13 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -8849,14 +8897,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8875,19 +8923,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -8936,7 +8984,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -8948,7 +8996,7 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -8965,10 +9013,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8994,10 +9042,10 @@
         <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9024,13 +9072,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9048,7 +9096,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>88</v>
@@ -9077,10 +9125,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9106,13 +9154,13 @@
         <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9162,7 +9210,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>88</v>
@@ -9191,10 +9239,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9217,15 +9265,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9274,7 +9324,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9303,10 +9353,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9329,15 +9379,17 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9386,7 +9438,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9415,10 +9467,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9441,15 +9493,17 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -9498,7 +9552,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9527,10 +9581,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9553,15 +9607,17 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9610,7 +9666,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9639,10 +9695,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9665,13 +9721,13 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9722,7 +9778,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -9731,7 +9787,7 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
@@ -9740,7 +9796,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -9751,10 +9807,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9777,13 +9833,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9834,7 +9890,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -9852,7 +9908,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -9863,14 +9919,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9889,16 +9945,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9936,19 +9992,19 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -9960,13 +10016,13 @@
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -9977,14 +10033,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10003,19 +10059,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10064,7 +10120,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10076,7 +10132,7 @@
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -10093,10 +10149,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10119,15 +10175,17 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10176,7 +10234,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -10205,10 +10263,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10234,12 +10292,14 @@
         <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10288,7 +10348,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10317,10 +10377,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10343,16 +10403,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10402,7 +10462,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10431,10 +10491,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10457,16 +10517,16 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10516,7 +10576,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10545,10 +10605,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10571,16 +10631,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10630,7 +10690,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -10648,7 +10708,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -10659,13 +10719,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>78</v>
@@ -10687,13 +10747,13 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10744,7 +10804,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -10753,16 +10813,16 @@
         <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -10773,10 +10833,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10799,13 +10859,13 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10856,7 +10916,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -10874,7 +10934,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -10885,14 +10945,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10911,16 +10971,16 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10958,19 +11018,19 @@
         <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -10982,13 +11042,13 @@
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -10999,14 +11059,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11025,19 +11085,19 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11086,7 +11146,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11098,7 +11158,7 @@
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -11115,10 +11175,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11144,10 +11204,10 @@
         <v>78</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11198,7 +11258,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11210,7 +11270,7 @@
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -11227,10 +11287,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11256,13 +11316,13 @@
         <v>102</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11312,7 +11372,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11341,10 +11401,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11367,13 +11427,13 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11424,7 +11484,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -11442,7 +11502,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -11453,10 +11513,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11479,13 +11539,13 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11536,7 +11596,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -11545,7 +11605,7 @@
         <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>100</v>
@@ -11554,7 +11614,7 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -11565,10 +11625,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11591,13 +11651,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11648,7 +11708,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -11666,7 +11726,7 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -11677,14 +11737,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11703,16 +11763,16 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11750,19 +11810,19 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -11774,13 +11834,13 @@
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -11791,14 +11851,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11817,19 +11877,19 @@
         <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -11878,7 +11938,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -11890,7 +11950,7 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -11907,10 +11967,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11936,13 +11996,13 @@
         <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11968,13 +12028,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -11992,7 +12052,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12021,10 +12081,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12047,16 +12107,16 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12106,7 +12166,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12135,10 +12195,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12161,13 +12221,13 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12218,7 +12278,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12227,7 +12287,7 @@
         <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>100</v>
@@ -12236,7 +12296,7 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -12247,10 +12307,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12273,13 +12333,13 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12330,7 +12390,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -12348,7 +12408,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -12359,14 +12419,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12385,16 +12445,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12432,19 +12492,19 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -12456,13 +12516,13 @@
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -12473,14 +12533,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12499,19 +12559,19 @@
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -12560,7 +12620,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -12572,7 +12632,7 @@
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -12589,10 +12649,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12618,10 +12678,10 @@
         <v>108</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12648,13 +12708,13 @@
         <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
@@ -12672,7 +12732,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>88</v>
@@ -12701,10 +12761,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12730,13 +12790,13 @@
         <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12786,7 +12846,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>88</v>
@@ -12815,10 +12875,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12841,15 +12901,17 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -12898,7 +12960,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -12927,10 +12989,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12953,15 +13015,17 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -13010,7 +13074,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13039,10 +13103,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13065,15 +13129,17 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -13122,7 +13188,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13151,10 +13217,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13177,15 +13243,17 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -13234,7 +13302,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13263,10 +13331,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13289,13 +13357,13 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13346,7 +13414,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -13355,7 +13423,7 @@
         <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>100</v>
@@ -13364,7 +13432,7 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -13375,10 +13443,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13401,13 +13469,13 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13458,7 +13526,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -13476,7 +13544,7 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -13487,14 +13555,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13513,16 +13581,16 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13560,19 +13628,19 @@
         <v>78</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -13584,13 +13652,13 @@
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -13601,14 +13669,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13627,19 +13695,19 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -13688,7 +13756,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -13700,7 +13768,7 @@
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>78</v>
@@ -13717,10 +13785,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13743,15 +13811,17 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -13800,7 +13870,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>88</v>
@@ -13829,10 +13899,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13858,12 +13928,14 @@
         <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -13912,7 +13984,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -13941,10 +14013,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13967,16 +14039,16 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14026,7 +14098,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14055,10 +14127,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14081,16 +14153,16 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14140,7 +14212,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14169,10 +14241,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14195,16 +14267,16 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14254,7 +14326,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -14272,7 +14344,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -14283,13 +14355,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>78</v>
@@ -14311,13 +14383,13 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14368,7 +14440,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -14377,16 +14449,16 @@
         <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -14397,10 +14469,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14423,13 +14495,13 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14480,7 +14552,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -14498,7 +14570,7 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
@@ -14509,14 +14581,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -14535,16 +14607,16 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14582,19 +14654,19 @@
         <v>78</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -14606,13 +14678,13 @@
         <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
@@ -14623,14 +14695,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -14649,19 +14721,19 @@
         <v>89</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -14710,7 +14782,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -14722,7 +14794,7 @@
         <v>78</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>78</v>
@@ -14739,10 +14811,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14768,10 +14840,10 @@
         <v>78</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14822,7 +14894,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -14834,7 +14906,7 @@
         <v>78</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>78</v>
@@ -14851,10 +14923,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14880,13 +14952,13 @@
         <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -14936,7 +15008,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -14965,10 +15037,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14991,16 +15063,16 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15050,7 +15122,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15068,7 +15140,7 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>78</v>
@@ -15079,10 +15151,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15105,13 +15177,13 @@
         <v>89</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15162,7 +15234,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -15171,7 +15243,7 @@
         <v>88</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>100</v>
@@ -15180,7 +15252,7 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -15191,10 +15263,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15217,13 +15289,13 @@
         <v>78</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15274,7 +15346,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -15292,7 +15364,7 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -15303,14 +15375,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -15329,16 +15401,16 @@
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -15376,19 +15448,19 @@
         <v>78</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -15400,13 +15472,13 @@
         <v>78</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
@@ -15417,14 +15489,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -15443,19 +15515,19 @@
         <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -15504,7 +15576,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -15516,7 +15588,7 @@
         <v>78</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>78</v>
@@ -15533,10 +15605,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15562,13 +15634,13 @@
         <v>108</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15594,13 +15666,13 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>78</v>
@@ -15618,7 +15690,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -15647,10 +15719,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15673,16 +15745,16 @@
         <v>89</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -15732,7 +15804,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -15761,10 +15833,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15787,13 +15859,13 @@
         <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15844,7 +15916,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -15853,7 +15925,7 @@
         <v>88</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>100</v>
@@ -15862,7 +15934,7 @@
         <v>78</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>78</v>
@@ -15873,10 +15945,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15899,13 +15971,13 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -15956,7 +16028,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -15974,7 +16046,7 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
@@ -15985,14 +16057,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16011,16 +16083,16 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16058,19 +16130,19 @@
         <v>78</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16082,13 +16154,13 @@
         <v>78</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>78</v>
@@ -16099,14 +16171,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -16125,19 +16197,19 @@
         <v>89</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -16186,7 +16258,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -16198,7 +16270,7 @@
         <v>78</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>78</v>
@@ -16215,10 +16287,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16244,10 +16316,10 @@
         <v>108</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -16274,13 +16346,13 @@
         <v>78</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>78</v>
@@ -16298,7 +16370,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>88</v>
@@ -16327,10 +16399,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16356,13 +16428,13 @@
         <v>102</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -16412,7 +16484,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>88</v>
@@ -16441,10 +16513,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16467,15 +16539,17 @@
         <v>89</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -16524,7 +16598,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -16553,10 +16627,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16579,15 +16653,17 @@
         <v>89</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -16636,7 +16712,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -16665,10 +16741,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16691,15 +16767,17 @@
         <v>89</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N134" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -16748,7 +16826,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -16777,10 +16855,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16803,15 +16881,17 @@
         <v>89</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N135" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -16860,7 +16940,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -16889,10 +16969,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16915,13 +16995,13 @@
         <v>89</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -16972,7 +17052,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -16981,7 +17061,7 @@
         <v>88</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>100</v>
@@ -16990,7 +17070,7 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>78</v>
@@ -17001,10 +17081,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17027,13 +17107,13 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -17084,7 +17164,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -17102,7 +17182,7 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>78</v>
@@ -17113,14 +17193,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -17139,16 +17219,16 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -17186,19 +17266,19 @@
         <v>78</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -17210,13 +17290,13 @@
         <v>78</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>78</v>
@@ -17227,14 +17307,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -17253,19 +17333,19 @@
         <v>89</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
@@ -17314,7 +17394,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -17326,7 +17406,7 @@
         <v>78</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>78</v>
@@ -17343,10 +17423,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17369,15 +17449,17 @@
         <v>89</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N140" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -17426,7 +17508,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>88</v>
@@ -17455,10 +17537,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17484,12 +17566,14 @@
         <v>102</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -17538,7 +17622,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -17567,10 +17651,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17593,16 +17677,16 @@
         <v>89</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -17652,7 +17736,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -17681,10 +17765,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17707,16 +17791,16 @@
         <v>89</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -17766,7 +17850,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -17795,10 +17879,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17821,16 +17905,16 @@
         <v>89</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -17880,7 +17964,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -17898,7 +17982,7 @@
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>78</v>
@@ -17909,10 +17993,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17935,19 +18019,19 @@
         <v>89</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -17996,7 +18080,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -18005,7 +18089,7 @@
         <v>88</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>100</v>
@@ -18014,7 +18098,7 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>78</v>
